--- a/Variaveis/Variaveis_selecionadas.xlsx
+++ b/Variaveis/Variaveis_selecionadas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\docs_mariana\ProjetosGit\TCC\Variaveis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB57F8D2-FFE3-4B9A-85BA-A0E10B79406B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D23D77F-107A-491A-9B8C-D0AA02648DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FADD9055-85FA-4F14-BFAE-A4B4B6C14256}"/>
+    <workbookView xWindow="28680" yWindow="2610" windowWidth="21840" windowHeight="13020" firstSheet="1" activeTab="1" xr2:uid="{FADD9055-85FA-4F14-BFAE-A4B4B6C14256}"/>
   </bookViews>
   <sheets>
     <sheet name="bloco 1 - identificação" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="247">
   <si>
     <t>SIS</t>
   </si>
@@ -294,15 +294,9 @@
     <t>Acesso a energia e água</t>
   </si>
   <si>
-    <t>DT_CADASTRO_FAM</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
-    <t>Data do cadastramento da Família, formato YYYY-MM-DD</t>
-  </si>
-  <si>
     <t>CO_EST_CADASTRAL_FAM</t>
   </si>
   <si>
@@ -354,12 +348,6 @@
     <t>Segunda parte do código IBGE</t>
   </si>
   <si>
-    <t>DT_ATUALIZACAO_FAM ⁴</t>
-  </si>
-  <si>
-    <t>Data da última atualização da família dos dados considerados sensíveis à manutenção do cadastro no formato YYYY-MM-DD</t>
-  </si>
-  <si>
     <t>Regras qualidade cadastro</t>
   </si>
   <si>
@@ -784,6 +772,18 @@
   </si>
   <si>
     <t>000 Nenhuma</t>
+  </si>
+  <si>
+    <t>1.09</t>
+  </si>
+  <si>
+    <t>IN_FORMULARIO_SUP2_FAM</t>
+  </si>
+  <si>
+    <t>Formulário Suplementar 2</t>
+  </si>
+  <si>
+    <t>0 - Não</t>
   </si>
 </sst>
 </file>
@@ -835,7 +835,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -888,15 +888,94 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -946,15 +1025,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -994,53 +1064,56 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1054,43 +1127,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1108,16 +1175,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan1" xfId="2" xr:uid="{3C026F14-2A8B-4FFD-8F7A-D681B84BC496}"/>
-    <cellStyle name="Normal_Plan2" xfId="4" xr:uid="{F6F59C72-AFDB-44EA-BBFA-610B2423F9F2}"/>
+    <cellStyle name="Normal_Plan2" xfId="3" xr:uid="{F6F59C72-AFDB-44EA-BBFA-610B2423F9F2}"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{AF9A0B32-363E-4DDE-8C01-E8FB55E5AC11}"/>
-    <cellStyle name="Normal_Plan2_1 2" xfId="3" xr:uid="{3E84BFF4-C2B9-4F86-96A6-EAACDB9DD99E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1462,14 +1549,14 @@
       <c r="A1" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -1487,227 +1574,223 @@
       <c r="E2" s="14">
         <v>11</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="34"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="A3" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="C3" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="14">
-        <v>8</v>
-      </c>
-      <c r="F3" s="34" t="s">
+      <c r="D3" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="37">
+        <v>1</v>
+      </c>
+      <c r="F3" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="34"/>
+      <c r="G3" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" s="40" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="36"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="36"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="34" t="s">
+      <c r="C7" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E7" s="16">
+        <v>9</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="31"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="33">
         <v>1</v>
       </c>
-      <c r="F4" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="37"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="37"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="16">
-        <v>9</v>
-      </c>
-      <c r="F8" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="G8" s="39"/>
+      <c r="F8" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="39" t="s">
+      <c r="A9" s="36"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="41">
+      <c r="C10" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="15" t="s">
-        <v>48</v>
-      </c>
+      <c r="E10" s="16">
+        <v>2</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="31"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>1</v>
       </c>
       <c r="E11" s="16">
-        <v>2</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="39"/>
+        <v>5</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="31"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="15" t="s">
+      <c r="A12" s="73" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="69" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="69" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="70">
         <v>1</v>
       </c>
-      <c r="E12" s="16">
-        <v>5</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="39"/>
-    </row>
-    <row r="13" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="19">
-        <v>8</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" s="38"/>
+      <c r="F12" s="69" t="s">
+        <v>245</v>
+      </c>
+      <c r="G12" s="71" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="74"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="71" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="F4:F7"/>
+  <mergeCells count="23">
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -1730,14 +1813,14 @@
       <c r="A1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -1761,10 +1844,10 @@
       <c r="G2" s="42"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="41" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="42" t="s">
@@ -1773,7 +1856,7 @@
       <c r="D3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="43">
         <v>1</v>
       </c>
       <c r="F3" s="42" t="s">
@@ -1784,21 +1867,21 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="43"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="42"/>
       <c r="D4" s="42"/>
-      <c r="E4" s="44"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="42"/>
       <c r="G4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="41" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="42" t="s">
@@ -1807,7 +1890,7 @@
       <c r="D5" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="43">
         <v>1</v>
       </c>
       <c r="F5" s="42" t="s">
@@ -1818,29 +1901,29 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
-      <c r="B6" s="43"/>
+      <c r="A6" s="40"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
-      <c r="E6" s="44"/>
+      <c r="E6" s="43"/>
       <c r="F6" s="42"/>
       <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="40"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
-      <c r="E7" s="44"/>
+      <c r="E7" s="43"/>
       <c r="F7" s="42"/>
       <c r="G7" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="46">
+      <c r="A8" s="40">
         <v>9</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -1858,10 +1941,10 @@
       <c r="F8" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="45"/>
+      <c r="G8" s="44"/>
     </row>
     <row r="9" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A9" s="46"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="8" t="s">
         <v>20</v>
       </c>
@@ -1877,13 +1960,13 @@
       <c r="F9" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="45"/>
+      <c r="G9" s="44"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="41" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="42" t="s">
@@ -1892,7 +1975,7 @@
       <c r="D10" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="43">
         <v>1</v>
       </c>
       <c r="F10" s="42" t="s">
@@ -1903,76 +1986,76 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="46"/>
-      <c r="B11" s="43"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
-      <c r="E11" s="44"/>
+      <c r="E11" s="43"/>
       <c r="F11" s="42"/>
       <c r="G11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
-      <c r="B12" s="43"/>
+      <c r="A12" s="40"/>
+      <c r="B12" s="41"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
-      <c r="E12" s="44"/>
+      <c r="E12" s="43"/>
       <c r="F12" s="42"/>
       <c r="G12" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="46"/>
-      <c r="B13" s="43"/>
+      <c r="A13" s="40"/>
+      <c r="B13" s="41"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
-      <c r="E13" s="44"/>
+      <c r="E13" s="43"/>
       <c r="F13" s="42"/>
       <c r="G13" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A14" s="46"/>
-      <c r="B14" s="43"/>
+      <c r="A14" s="40"/>
+      <c r="B14" s="41"/>
       <c r="C14" s="42"/>
       <c r="D14" s="42"/>
-      <c r="E14" s="44"/>
+      <c r="E14" s="43"/>
       <c r="F14" s="42"/>
       <c r="G14" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="46"/>
-      <c r="B15" s="43"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="42"/>
       <c r="D15" s="42"/>
-      <c r="E15" s="44"/>
+      <c r="E15" s="43"/>
       <c r="F15" s="42"/>
       <c r="G15" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="46"/>
-      <c r="B16" s="43"/>
+      <c r="A16" s="40"/>
+      <c r="B16" s="41"/>
       <c r="C16" s="42"/>
       <c r="D16" s="42"/>
-      <c r="E16" s="44"/>
+      <c r="E16" s="43"/>
       <c r="F16" s="42"/>
       <c r="G16" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="41" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="42" t="s">
@@ -1981,7 +2064,7 @@
       <c r="D17" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="43">
         <v>1</v>
       </c>
       <c r="F17" s="42" t="s">
@@ -1992,87 +2075,87 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A18" s="46"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="40"/>
+      <c r="B18" s="41"/>
       <c r="C18" s="42"/>
       <c r="D18" s="42"/>
-      <c r="E18" s="44"/>
+      <c r="E18" s="43"/>
       <c r="F18" s="42"/>
       <c r="G18" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="46"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="40"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
-      <c r="E19" s="44"/>
+      <c r="E19" s="43"/>
       <c r="F19" s="42"/>
       <c r="G19" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="46"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="40"/>
+      <c r="B20" s="41"/>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
-      <c r="E20" s="44"/>
+      <c r="E20" s="43"/>
       <c r="F20" s="42"/>
       <c r="G20" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="46"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="40"/>
+      <c r="B21" s="41"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
-      <c r="E21" s="44"/>
+      <c r="E21" s="43"/>
       <c r="F21" s="42"/>
       <c r="G21" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="46"/>
-      <c r="B22" s="43"/>
+      <c r="A22" s="40"/>
+      <c r="B22" s="41"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
-      <c r="E22" s="44"/>
+      <c r="E22" s="43"/>
       <c r="F22" s="42"/>
       <c r="G22" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="46"/>
-      <c r="B23" s="43"/>
+      <c r="A23" s="40"/>
+      <c r="B23" s="41"/>
       <c r="C23" s="42"/>
       <c r="D23" s="42"/>
-      <c r="E23" s="44"/>
+      <c r="E23" s="43"/>
       <c r="F23" s="42"/>
       <c r="G23" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="46"/>
-      <c r="B24" s="43"/>
+      <c r="A24" s="40"/>
+      <c r="B24" s="41"/>
       <c r="C24" s="42"/>
       <c r="D24" s="42"/>
-      <c r="E24" s="44"/>
+      <c r="E24" s="43"/>
       <c r="F24" s="42"/>
       <c r="G24" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="41" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="42" t="s">
@@ -2081,7 +2164,7 @@
       <c r="D25" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="44">
+      <c r="E25" s="43">
         <v>1</v>
       </c>
       <c r="F25" s="42" t="s">
@@ -2092,21 +2175,21 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="46"/>
-      <c r="B26" s="43"/>
+      <c r="A26" s="40"/>
+      <c r="B26" s="41"/>
       <c r="C26" s="42"/>
       <c r="D26" s="42"/>
-      <c r="E26" s="44"/>
+      <c r="E26" s="43"/>
       <c r="F26" s="42"/>
       <c r="G26" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="41" t="s">
         <v>49</v>
       </c>
       <c r="C27" s="42" t="s">
@@ -2115,7 +2198,7 @@
       <c r="D27" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="44">
+      <c r="E27" s="43">
         <v>1</v>
       </c>
       <c r="F27" s="42" t="s">
@@ -2126,43 +2209,43 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="46"/>
-      <c r="B28" s="43"/>
+      <c r="A28" s="40"/>
+      <c r="B28" s="41"/>
       <c r="C28" s="42"/>
       <c r="D28" s="42"/>
-      <c r="E28" s="44"/>
+      <c r="E28" s="43"/>
       <c r="F28" s="42"/>
       <c r="G28" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="46"/>
-      <c r="B29" s="43"/>
+      <c r="A29" s="40"/>
+      <c r="B29" s="41"/>
       <c r="C29" s="42"/>
       <c r="D29" s="42"/>
-      <c r="E29" s="44"/>
+      <c r="E29" s="43"/>
       <c r="F29" s="42"/>
       <c r="G29" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="46"/>
-      <c r="B30" s="43"/>
+      <c r="A30" s="40"/>
+      <c r="B30" s="41"/>
       <c r="C30" s="42"/>
       <c r="D30" s="42"/>
-      <c r="E30" s="44"/>
+      <c r="E30" s="43"/>
       <c r="F30" s="42"/>
       <c r="G30" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="41" t="s">
         <v>56</v>
       </c>
       <c r="C31" s="42" t="s">
@@ -2171,7 +2254,7 @@
       <c r="D31" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="43">
         <v>1</v>
       </c>
       <c r="F31" s="42" t="s">
@@ -2182,21 +2265,21 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="46"/>
-      <c r="B32" s="43"/>
+      <c r="A32" s="40"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="42"/>
       <c r="D32" s="42"/>
-      <c r="E32" s="44"/>
+      <c r="E32" s="43"/>
       <c r="F32" s="42"/>
       <c r="G32" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B33" s="43" t="s">
+      <c r="B33" s="41" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="42" t="s">
@@ -2205,7 +2288,7 @@
       <c r="D33" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="44">
+      <c r="E33" s="43">
         <v>1</v>
       </c>
       <c r="F33" s="42" t="s">
@@ -2216,65 +2299,65 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="46"/>
-      <c r="B34" s="43"/>
+      <c r="A34" s="40"/>
+      <c r="B34" s="41"/>
       <c r="C34" s="42"/>
       <c r="D34" s="42"/>
-      <c r="E34" s="44"/>
+      <c r="E34" s="43"/>
       <c r="F34" s="42"/>
       <c r="G34" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="46"/>
-      <c r="B35" s="43"/>
+      <c r="A35" s="40"/>
+      <c r="B35" s="41"/>
       <c r="C35" s="42"/>
       <c r="D35" s="42"/>
-      <c r="E35" s="44"/>
+      <c r="E35" s="43"/>
       <c r="F35" s="42"/>
       <c r="G35" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="46"/>
-      <c r="B36" s="43"/>
+      <c r="A36" s="40"/>
+      <c r="B36" s="41"/>
       <c r="C36" s="42"/>
       <c r="D36" s="42"/>
-      <c r="E36" s="44"/>
+      <c r="E36" s="43"/>
       <c r="F36" s="42"/>
       <c r="G36" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A37" s="46"/>
-      <c r="B37" s="43"/>
+      <c r="A37" s="40"/>
+      <c r="B37" s="41"/>
       <c r="C37" s="42"/>
       <c r="D37" s="42"/>
-      <c r="E37" s="44"/>
+      <c r="E37" s="43"/>
       <c r="F37" s="42"/>
       <c r="G37" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="46"/>
-      <c r="B38" s="43"/>
+      <c r="A38" s="40"/>
+      <c r="B38" s="41"/>
       <c r="C38" s="42"/>
       <c r="D38" s="42"/>
-      <c r="E38" s="44"/>
+      <c r="E38" s="43"/>
       <c r="F38" s="42"/>
       <c r="G38" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A39" s="46" t="s">
+      <c r="A39" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="B39" s="43" t="s">
+      <c r="B39" s="41" t="s">
         <v>68</v>
       </c>
       <c r="C39" s="42" t="s">
@@ -2283,7 +2366,7 @@
       <c r="D39" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="44">
+      <c r="E39" s="43">
         <v>1</v>
       </c>
       <c r="F39" s="42" t="s">
@@ -2294,55 +2377,55 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A40" s="46"/>
-      <c r="B40" s="43"/>
+      <c r="A40" s="40"/>
+      <c r="B40" s="41"/>
       <c r="C40" s="42"/>
       <c r="D40" s="42"/>
-      <c r="E40" s="44"/>
+      <c r="E40" s="43"/>
       <c r="F40" s="42"/>
       <c r="G40" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="46"/>
-      <c r="B41" s="43"/>
+      <c r="A41" s="40"/>
+      <c r="B41" s="41"/>
       <c r="C41" s="42"/>
       <c r="D41" s="42"/>
-      <c r="E41" s="44"/>
+      <c r="E41" s="43"/>
       <c r="F41" s="42"/>
       <c r="G41" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A42" s="46"/>
-      <c r="B42" s="43"/>
+      <c r="A42" s="40"/>
+      <c r="B42" s="41"/>
       <c r="C42" s="42"/>
       <c r="D42" s="42"/>
-      <c r="E42" s="44"/>
+      <c r="E42" s="43"/>
       <c r="F42" s="42"/>
       <c r="G42" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="46"/>
-      <c r="B43" s="43"/>
+      <c r="A43" s="40"/>
+      <c r="B43" s="41"/>
       <c r="C43" s="42"/>
       <c r="D43" s="42"/>
-      <c r="E43" s="44"/>
+      <c r="E43" s="43"/>
       <c r="F43" s="42"/>
       <c r="G43" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="46"/>
-      <c r="B44" s="43"/>
+      <c r="A44" s="40"/>
+      <c r="B44" s="41"/>
       <c r="C44" s="42"/>
       <c r="D44" s="42"/>
-      <c r="E44" s="44"/>
+      <c r="E44" s="43"/>
       <c r="F44" s="42"/>
       <c r="G44" s="1" t="s">
         <v>67</v>
@@ -2357,12 +2440,12 @@
       <c r="G45" s="5"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B46" s="47"/>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B47" s="3"/>
@@ -2374,8 +2457,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="B10:B16"/>
+    <mergeCell ref="C10:C16"/>
+    <mergeCell ref="D10:D16"/>
+    <mergeCell ref="E10:E16"/>
+    <mergeCell ref="F10:F16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:C24"/>
+    <mergeCell ref="D17:D24"/>
+    <mergeCell ref="E17:E24"/>
+    <mergeCell ref="F17:F24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="A39:A44"/>
+    <mergeCell ref="A31:A32"/>
     <mergeCell ref="B33:B38"/>
     <mergeCell ref="A33:A38"/>
+    <mergeCell ref="F27:F30"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="D27:D30"/>
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="D33:D38"/>
+    <mergeCell ref="E33:E38"/>
+    <mergeCell ref="F33:F38"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
     <mergeCell ref="B46:G46"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A3:A4"/>
@@ -2390,50 +2515,8 @@
     <mergeCell ref="D39:D44"/>
     <mergeCell ref="E39:E44"/>
     <mergeCell ref="F39:F44"/>
-    <mergeCell ref="A39:A44"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="C33:C38"/>
-    <mergeCell ref="D33:D38"/>
-    <mergeCell ref="E33:E38"/>
-    <mergeCell ref="F33:F38"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="D27:D30"/>
-    <mergeCell ref="E27:E30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F27:F30"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:C24"/>
-    <mergeCell ref="D17:D24"/>
-    <mergeCell ref="E17:E24"/>
-    <mergeCell ref="F17:F24"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B10:B16"/>
-    <mergeCell ref="C10:C16"/>
-    <mergeCell ref="D10:D16"/>
-    <mergeCell ref="E10:E16"/>
-    <mergeCell ref="F10:F16"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2453,14 +2536,14 @@
       <c r="A1" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -2469,85 +2552,85 @@
       <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="17">
         <v>11</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="50"/>
+      <c r="G2" s="48"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="D3" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="49">
+        <v>1</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="36"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="D5" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="45">
+        <v>1</v>
+      </c>
+      <c r="F5" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="51">
-        <v>1</v>
-      </c>
-      <c r="F3" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="G3" s="21" t="s">
+      <c r="G5" s="18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="53" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="53">
-        <v>1</v>
-      </c>
-      <c r="F5" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>47</v>
-      </c>
-    </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="21" t="s">
+      <c r="A6" s="36"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="18" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2556,42 +2639,42 @@
         <v>80</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="18">
         <v>2</v>
       </c>
-      <c r="F7" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="G7" s="54"/>
+      <c r="F7" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="G7" s="46"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>80</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="D8" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="18">
         <v>2</v>
       </c>
-      <c r="F8" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="G8" s="54"/>
+      <c r="F8" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2627,407 +2710,417 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="23">
         <v>11</v>
       </c>
-      <c r="F2" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" s="56"/>
+      <c r="F2" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="60"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="23">
+        <v>11</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="60"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="59">
+        <v>1</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="53"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="53"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="53"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="23" t="s">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="53"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="59">
         <v>1</v>
       </c>
-      <c r="E3" s="26">
-        <v>11</v>
-      </c>
-      <c r="F3" s="55" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="56"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="55" t="s">
+      <c r="F10" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" s="53"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="23">
+        <v>8</v>
+      </c>
+      <c r="F12" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="57"/>
+    </row>
+    <row r="13" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A13" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="57">
+      <c r="E13" s="58">
+        <v>2</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="52"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="52"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="52"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="52"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="25" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="52"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="52"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="52"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="25" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="52"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="25" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="56">
         <v>1</v>
       </c>
-      <c r="F4" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="29" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="57">
-        <v>1</v>
-      </c>
-      <c r="F10" s="58" t="s">
-        <v>130</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="28" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="26">
-        <v>8</v>
-      </c>
-      <c r="F12" s="58" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="63"/>
-    </row>
-    <row r="13" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A13" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="64">
-        <v>2</v>
-      </c>
-      <c r="F13" s="58" t="s">
-        <v>138</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="28" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="61"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="28" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="61"/>
-      <c r="B17" s="59"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="28" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="61"/>
-      <c r="B18" s="59"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="28" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="61"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="28" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="28" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="28" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="61"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="28" t="s">
+      <c r="F24" s="54" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="61"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="28" t="s">
+      <c r="G24" s="20" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="59" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="52"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="55" t="s">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="52"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="58" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="62">
-        <v>1</v>
-      </c>
-      <c r="F24" s="55" t="s">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="52"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="G24" s="23" t="s">
+    </row>
+    <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="52"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="20" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="61"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="23" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="61"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="61"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="23" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="61"/>
-      <c r="B28" s="59"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="23" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="E4:E9"/>
+    <mergeCell ref="F4:F9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A13:A23"/>
     <mergeCell ref="A24:A28"/>
@@ -3044,16 +3137,6 @@
     <mergeCell ref="F13:F23"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="E4:E9"/>
-    <mergeCell ref="F4:F9"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3071,91 +3154,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="23">
         <v>11</v>
       </c>
-      <c r="F2" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" s="66"/>
+      <c r="F2" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="62"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="31" t="s">
+      <c r="C3" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="23">
         <v>11</v>
       </c>
-      <c r="F3" s="65" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="66"/>
+      <c r="F3" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="62"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="B4" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="65" t="s">
+      <c r="A4" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="61" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="57">
+      <c r="E4" s="59">
         <v>1</v>
       </c>
-      <c r="F4" s="65" t="s">
-        <v>161</v>
-      </c>
-      <c r="G4" s="31" t="s">
+      <c r="F4" s="61" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="61"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="31" t="s">
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="28" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3188,495 +3271,506 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="B2" s="22" t="s">
+      <c r="A2" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="23">
         <v>11</v>
       </c>
-      <c r="F2" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" s="56"/>
+      <c r="F2" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="60"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="B3" s="22" t="s">
+      <c r="A3" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="23">
         <v>11</v>
       </c>
-      <c r="F3" s="55" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="56"/>
+      <c r="F3" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="60"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="B4" s="67" t="s">
+      <c r="A4" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="59">
+        <v>1</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>160</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="52"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="D6" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="59">
+        <v>1</v>
+      </c>
+      <c r="F6" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="G6" s="20" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="52"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="52"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="52"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="57">
-        <v>1</v>
-      </c>
-      <c r="F4" s="55" t="s">
-        <v>164</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="61"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="B6" s="67" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>166</v>
-      </c>
-      <c r="D6" s="55" t="s">
+      <c r="E10" s="59">
+        <v>2</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="52"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="20" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="52"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="52"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="52"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="20" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="52"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="20" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="52"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A18" s="52"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A19" s="52"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="52"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="52"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A22" s="52"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="52"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="D24" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="57">
-        <v>1</v>
-      </c>
-      <c r="F6" s="55" t="s">
-        <v>167</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="61"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="23" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="61"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="23" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="61"/>
-      <c r="B9" s="67"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="23" t="s">
+      <c r="E24" s="59">
+        <v>2</v>
+      </c>
+      <c r="F24" s="54" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="67" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="52"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="55" t="s">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="52"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="D10" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="57">
-        <v>2</v>
-      </c>
-      <c r="F10" s="55" t="s">
-        <v>174</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="23" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="23" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="23" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="23" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="23" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="61"/>
-      <c r="B16" s="67"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="23" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="61"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="23" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A18" s="61"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="23" t="s">
+    </row>
+    <row r="27" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A27" s="52"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="20" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A28" s="52"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="20" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="52"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="20" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="52"/>
+      <c r="B30" s="63"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="20" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A31" s="52"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="20" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="52"/>
+      <c r="B32" s="63"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A33" s="52"/>
+      <c r="B33" s="63"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A34" s="52"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="20" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="52"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A36" s="52"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="20" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A19" s="61"/>
-      <c r="B19" s="67"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="23" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
-      <c r="B20" s="67"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="23" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A22" s="61"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="23" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="61"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="23" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="B24" s="67" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="57">
-        <v>2</v>
-      </c>
-      <c r="F24" s="55" t="s">
-        <v>191</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="61"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="23" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="61"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="23" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A27" s="61"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="23" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A28" s="61"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="61"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="23" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="61"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="23" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A31" s="61"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="23" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="61"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="23" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="52"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="20" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A33" s="61"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="23" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="52"/>
+      <c r="B38" s="64"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="20" t="s">
         <v>198</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A34" s="61"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="55"/>
-      <c r="D34" s="55"/>
-      <c r="E34" s="57"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="23" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="61"/>
-      <c r="B35" s="67"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="23" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A36" s="61"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="23" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="61"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="23" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="61"/>
-      <c r="B38" s="68"/>
-      <c r="C38" s="69"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="23" t="s">
-        <v>202</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B24:B38"/>
+    <mergeCell ref="C24:C38"/>
+    <mergeCell ref="D24:D38"/>
+    <mergeCell ref="E24:E38"/>
+    <mergeCell ref="F24:F38"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A9"/>
@@ -3693,17 +3787,6 @@
     <mergeCell ref="E6:E9"/>
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="B24:B38"/>
-    <mergeCell ref="C24:C38"/>
-    <mergeCell ref="D24:D38"/>
-    <mergeCell ref="E24:E38"/>
-    <mergeCell ref="F24:F38"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -3721,331 +3804,348 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="23">
         <v>11</v>
       </c>
-      <c r="F2" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" s="55"/>
+      <c r="F2" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="54"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="27">
         <v>11</v>
       </c>
-      <c r="F3" s="58" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="58"/>
+      <c r="F3" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="55"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="54" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="56">
+        <v>1</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="D6" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="56">
+        <v>1</v>
+      </c>
+      <c r="F6" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="G6" s="25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="52"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" s="54" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="62">
+      <c r="E8" s="56">
         <v>1</v>
       </c>
-      <c r="F4" s="58" t="s">
-        <v>207</v>
-      </c>
-      <c r="G4" s="28" t="s">
+      <c r="F8" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="G8" s="25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="61"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="28" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="52"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="61" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="59" t="s">
-        <v>208</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>209</v>
-      </c>
-      <c r="D6" s="55" t="s">
+      <c r="B10" s="53" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="62">
+      <c r="E10" s="56">
+        <v>2</v>
+      </c>
+      <c r="F10" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="52"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="25" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="52"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="25" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="52"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="25" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="52"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="52"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="25" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="52"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="25" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="52"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="25" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="52"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="25" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="52"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="25" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>225</v>
+      </c>
+      <c r="D21" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="56">
         <v>1</v>
       </c>
-      <c r="F6" s="58" t="s">
-        <v>210</v>
-      </c>
-      <c r="G6" s="28" t="s">
+      <c r="F21" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="G21" s="25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="61"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="59" t="s">
-        <v>211</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>212</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="62">
-        <v>1</v>
-      </c>
-      <c r="F8" s="58" t="s">
-        <v>213</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="61"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="59" t="s">
-        <v>214</v>
-      </c>
-      <c r="C10" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="62">
-        <v>2</v>
-      </c>
-      <c r="F10" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="B11" s="59"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="28" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="28" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="28" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="28" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="28" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="61"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="28" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="61"/>
-      <c r="B17" s="59"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="28" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="61"/>
-      <c r="B18" s="59"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="28" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="61"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="28" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="28" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="59" t="s">
-        <v>228</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>229</v>
-      </c>
-      <c r="D21" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="62">
-        <v>1</v>
-      </c>
-      <c r="F21" s="58" t="s">
-        <v>230</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>47</v>
-      </c>
-    </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="61"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="28" t="s">
+      <c r="A22" s="52"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="25" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="A10:A20"/>
     <mergeCell ref="A21:A22"/>
@@ -4062,23 +4162,6 @@
     <mergeCell ref="D10:D20"/>
     <mergeCell ref="E10:E20"/>
     <mergeCell ref="F10:F20"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4097,257 +4180,257 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="23">
         <v>11</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="69"/>
+      <c r="G2" s="65"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="59" t="s">
+      <c r="A3" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="61" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="59">
+        <v>3</v>
+      </c>
+      <c r="F3" s="61" t="s">
+        <v>228</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="D3" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="57">
-        <v>3</v>
-      </c>
-      <c r="F3" s="65" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="52"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="67" t="s">
         <v>232</v>
       </c>
-      <c r="G3" s="33" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="52"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="65"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="52"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="30" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="61"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="33" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="52"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="24" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="61"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="33" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="52"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="60" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="61"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="71" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="52"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="65"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="52"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="60" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="61"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="69"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="61"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="33" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="52"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="65"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="52"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="24" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="61"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="27" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="52"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="60" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="61"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="56" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="52"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="65"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="52"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="60" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="B11" s="59"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="69"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="56" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="52"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="65"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="52"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="60" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="69"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="27" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="52"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="65"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="24" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="56" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="52"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="24" t="s">
         <v>242</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="61"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="69"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="61"/>
-      <c r="B17" s="59"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="56" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="61"/>
-      <c r="B18" s="59"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="69"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="61"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="56" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="69"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="61"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="27" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="61"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="27" t="s">
-        <v>246</v>
       </c>
     </row>
   </sheetData>
